--- a/medical_surveys_questionnaires/045_end_of_life_care_communication_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/045_end_of_life_care_communication_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>communication_frequency</t>
+          <t>communication_frequency_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Communication Frequency</t>
+          <t>Communication Frequency 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>communication_method</t>
+          <t>communication_method_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Communication Method</t>
+          <t>Communication Method 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>communication_quality</t>
+          <t>communication_quality_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Communication Quality</t>
+          <t>Communication Quality 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pain_management</t>
+          <t>pain_management_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pain Management</t>
+          <t>Pain Management 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>emotional_support_services</t>
+          <t>emotional_support_services_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emotional Support Services</t>
+          <t>Emotional Support Services 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
   <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1579,7 +1579,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1596,7 +1596,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,7 +1647,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>communication_method_choices</t>
+          <t>communication_method_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>communication_method_choices</t>
+          <t>communication_method_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1698,7 +1698,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>communication_method_choices</t>
+          <t>communication_method_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>communication_method_choices</t>
+          <t>communication_method_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1732,7 +1732,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>emotional_support_services_choices</t>
+          <t>emotional_support_services_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>emotional_support_services_choices</t>
+          <t>emotional_support_services_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1766,7 +1766,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>emotional_support_services_choices</t>
+          <t>emotional_support_services_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
